--- a/salidas/empresas/FDX.xlsx
+++ b/salidas/empresas/FDX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>65.34455108642578</v>
+        <v>65.34454345703125</v>
       </c>
       <c r="C2" t="n">
         <v>81.50685119628906</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>69.27881622314453</v>
+        <v>69.27883148193359</v>
       </c>
       <c r="C3" t="n">
         <v>86.4141845703125</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>73.01338958740234</v>
+        <v>73.01334381103516</v>
       </c>
       <c r="C4" t="n">
         <v>91.00725555419922</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>74.42913055419922</v>
+        <v>74.42916870117188</v>
       </c>
       <c r="C5" t="n">
         <v>92.77195739746094</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>70.64079284667969</v>
+        <v>70.6407470703125</v>
       </c>
       <c r="C6" t="n">
         <v>88.04995727539062</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>75.61070251464844</v>
+        <v>75.61069488525391</v>
       </c>
       <c r="C7" t="n">
         <v>94.16599273681641</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>67.74941253662109</v>
+        <v>67.74945068359375</v>
       </c>
       <c r="C8" t="n">
         <v>84.37550354003906</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>65.36837768554688</v>
+        <v>65.36839294433594</v>
       </c>
       <c r="C9" t="n">
         <v>81.41015625</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>70.38095855712891</v>
+        <v>70.3809814453125</v>
       </c>
       <c r="C10" t="n">
         <v>87.57453918457031</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>74.17585754394531</v>
+        <v>74.17587280273438</v>
       </c>
       <c r="C11" t="n">
         <v>92.29653167724609</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>74.75221252441406</v>
+        <v>74.75222015380859</v>
       </c>
       <c r="C12" t="n">
         <v>93.01370239257812</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>70.39630889892578</v>
+        <v>70.39636993408203</v>
       </c>
       <c r="C13" t="n">
         <v>87.52619171142578</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>74.03215026855469</v>
+        <v>74.03214263916016</v>
       </c>
       <c r="C15" t="n">
         <v>92.04673767089844</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>69.68092346191406</v>
+        <v>69.68090057373047</v>
       </c>
       <c r="C16" t="n">
         <v>86.56728363037109</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>68.39016723632812</v>
+        <v>68.39013671875</v>
       </c>
       <c r="C17" t="n">
         <v>84.96373748779297</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>72.04290771484375</v>
+        <v>72.04293060302734</v>
       </c>
       <c r="C19" t="n">
         <v>89.41982269287109</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>71.89360046386719</v>
+        <v>71.89363098144531</v>
       </c>
       <c r="C20" t="n">
         <v>89.23448944091797</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>68.06674957275391</v>
+        <v>68.06675720214844</v>
       </c>
       <c r="C22" t="n">
         <v>84.40773773193359</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>67.15052795410156</v>
+        <v>67.15052032470703</v>
       </c>
       <c r="C23" t="n">
         <v>83.27155303955078</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>63.98601531982422</v>
+        <v>63.98600387573242</v>
       </c>
       <c r="C24" t="n">
         <v>79.34729766845703</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>58.00072479248047</v>
+        <v>58.0007209777832</v>
       </c>
       <c r="C25" t="n">
         <v>71.85334777832031</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>60.70009231567383</v>
+        <v>60.70009994506836</v>
       </c>
       <c r="C26" t="n">
         <v>75.19741821289062</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>57.32424926757812</v>
+        <v>57.32426452636719</v>
       </c>
       <c r="C27" t="n">
         <v>71.01531219482422</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>60.34521484375</v>
+        <v>60.34523010253906</v>
       </c>
       <c r="C28" t="n">
         <v>74.67365264892578</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>62.42900466918945</v>
+        <v>62.42902374267578</v>
       </c>
       <c r="C29" t="n">
         <v>77.25221252441406</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>59.72010040283203</v>
+        <v>59.7200813293457</v>
       </c>
       <c r="C30" t="n">
         <v>73.90007781982422</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>51.36937713623047</v>
+        <v>51.36938095092773</v>
       </c>
       <c r="C31" t="n">
         <v>63.48912048339844</v>
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>53.99685287475586</v>
+        <v>53.99684143066406</v>
       </c>
       <c r="C33" t="n">
         <v>66.73650360107422</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>51.60136413574219</v>
+        <v>51.60134124755859</v>
       </c>
       <c r="C34" t="n">
         <v>63.69057083129883</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>42.6768798828125</v>
+        <v>42.67687606811523</v>
       </c>
       <c r="C35" t="n">
         <v>52.67526245117188</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>46.12393188476562</v>
+        <v>46.12392807006836</v>
       </c>
       <c r="C36" t="n">
         <v>56.92989349365234</v>
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>33.31381225585938</v>
+        <v>33.31380462646484</v>
       </c>
       <c r="C38" t="n">
         <v>41.04754257202148</v>
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>29.1854133605957</v>
+        <v>29.18541526794434</v>
       </c>
       <c r="C40" t="n">
         <v>35.85012054443359</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>36.7097282409668</v>
+        <v>36.709716796875</v>
       </c>
       <c r="C41" t="n">
         <v>45.09266662597656</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>36.36203765869141</v>
+        <v>36.36205291748047</v>
       </c>
       <c r="C42" t="n">
         <v>44.66559219360352</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>44.59730529785156</v>
+        <v>44.59730911254883</v>
       </c>
       <c r="C44" t="n">
         <v>54.66559219360352</v>
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>49.52573394775391</v>
+        <v>49.52572250366211</v>
       </c>
       <c r="C46" t="n">
         <v>60.61240768432617</v>
@@ -1343,7 +1355,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1368,11 +1380,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>55.60287094116211</v>
+        <v>55.60285186767578</v>
       </c>
       <c r="C48" t="n">
         <v>68.04995727539062</v>
@@ -1393,11 +1405,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>55.01243209838867</v>
+        <v>55.01246643066406</v>
       </c>
       <c r="C49" t="n">
         <v>67.24415588378906</v>
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>51.65039443969727</v>
+        <v>51.65040588378906</v>
       </c>
       <c r="C50" t="n">
         <v>63.13456726074219</v>
@@ -1443,11 +1455,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>55.87604141235352</v>
+        <v>55.87604522705078</v>
       </c>
       <c r="C51" t="n">
         <v>68.29975891113281</v>
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>61.65004348754883</v>
+        <v>61.64998245239258</v>
       </c>
       <c r="C52" t="n">
         <v>75.26188659667969</v>
@@ -1493,11 +1505,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>59.41239166259766</v>
+        <v>59.41239547729492</v>
       </c>
       <c r="C53" t="n">
         <v>72.53022003173828</v>
@@ -1518,11 +1530,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>55.10875701904297</v>
+        <v>55.1087532043457</v>
       </c>
       <c r="C54" t="n">
         <v>67.27639007568359</v>
@@ -1543,11 +1555,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>46.34535980224609</v>
+        <v>46.34537124633789</v>
       </c>
       <c r="C55" t="n">
         <v>56.4947624206543</v>
@@ -1568,11 +1580,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>54.56866455078125</v>
+        <v>54.56867599487305</v>
       </c>
       <c r="C56" t="n">
         <v>66.51893615722656</v>
@@ -1597,11 +1609,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>51.59401702880859</v>
+        <v>51.59401321411133</v>
       </c>
       <c r="C57" t="n">
         <v>62.89282989501953</v>
@@ -1626,11 +1638,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>56.60161972045898</v>
+        <v>56.60157012939453</v>
       </c>
       <c r="C58" t="n">
         <v>68.89604949951172</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>58.07123184204102</v>
+        <v>58.07123947143555</v>
       </c>
       <c r="C59" t="n">
         <v>70.68492889404297</v>
@@ -1684,11 +1696,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>60.40673828125</v>
+        <v>60.40671920776367</v>
       </c>
       <c r="C60" t="n">
         <v>73.42465972900391</v>
@@ -1713,11 +1725,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>61.65966415405273</v>
+        <v>61.65967178344727</v>
       </c>
       <c r="C61" t="n">
         <v>74.94762420654297</v>
@@ -1742,11 +1754,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>59.87638854980469</v>
+        <v>59.87636566162109</v>
       </c>
       <c r="C62" t="n">
         <v>72.78001403808594</v>
@@ -1771,11 +1783,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>59.677490234375</v>
+        <v>59.67751312255859</v>
       </c>
       <c r="C63" t="n">
         <v>72.53827667236328</v>
@@ -1800,11 +1812,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>62.1025390625</v>
+        <v>62.10256576538086</v>
       </c>
       <c r="C64" t="n">
         <v>75.38275909423828</v>
@@ -1829,11 +1841,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>63.5098876953125</v>
+        <v>63.50991821289062</v>
       </c>
       <c r="C65" t="n">
         <v>77.09105682373047</v>
@@ -1858,11 +1870,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>62.16227340698242</v>
+        <v>62.16228866577148</v>
       </c>
       <c r="C66" t="n">
         <v>75.45527648925781</v>
@@ -1887,11 +1899,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>63.05928421020508</v>
+        <v>63.05930328369141</v>
       </c>
       <c r="C67" t="n">
         <v>76.4302978515625</v>
@@ -1916,11 +1928,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>57.76057815551758</v>
+        <v>57.76058959960938</v>
       </c>
       <c r="C68" t="n">
         <v>70.008056640625</v>
@@ -1945,11 +1957,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>52.33556747436523</v>
+        <v>52.33556365966797</v>
       </c>
       <c r="C69" t="n">
         <v>63.43271636962891</v>
@@ -1974,11 +1986,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>45.07265090942383</v>
+        <v>45.07263946533203</v>
       </c>
       <c r="C70" t="n">
         <v>54.53666305541992</v>
@@ -2003,11 +2015,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>54.49607467651367</v>
+        <v>54.4960823059082</v>
       </c>
       <c r="C71" t="n">
         <v>65.93875885009766</v>
@@ -2032,7 +2044,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2061,11 +2073,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>55.70270919799805</v>
+        <v>55.70270538330078</v>
       </c>
       <c r="C73" t="n">
         <v>67.29250335693359</v>
@@ -2090,11 +2102,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>61.02553176879883</v>
+        <v>61.0255012512207</v>
       </c>
       <c r="C74" t="n">
         <v>73.72280120849609</v>
@@ -2119,11 +2131,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>60.02499389648438</v>
+        <v>60.02500152587891</v>
       </c>
       <c r="C75" t="n">
         <v>72.51409912109375</v>
@@ -2148,11 +2160,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>61.42797088623047</v>
+        <v>61.42797470092773</v>
       </c>
       <c r="C76" t="n">
         <v>74.10153198242188</v>
@@ -2177,11 +2189,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>58.94307327270508</v>
+        <v>58.94306945800781</v>
       </c>
       <c r="C77" t="n">
         <v>71.10395050048828</v>
@@ -2206,11 +2218,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>59.54426956176758</v>
+        <v>59.54424667358398</v>
       </c>
       <c r="C78" t="n">
         <v>71.82917022705078</v>
@@ -2235,7 +2247,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2264,11 +2276,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>60.41726684570312</v>
+        <v>60.41725540161133</v>
       </c>
       <c r="C80" t="n">
         <v>72.76390075683594</v>
@@ -2293,11 +2305,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>58.63083267211914</v>
+        <v>58.63084411621094</v>
       </c>
       <c r="C81" t="n">
         <v>70.61241149902344</v>
@@ -2322,7 +2334,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2351,11 +2363,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>61.64858245849609</v>
+        <v>61.64858627319336</v>
       </c>
       <c r="C83" t="n">
         <v>74.12570190429688</v>
@@ -2380,11 +2392,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>60.09767532348633</v>
+        <v>60.09763336181641</v>
       </c>
       <c r="C84" t="n">
         <v>72.1434326171875</v>
@@ -2409,11 +2421,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>61.56772613525391</v>
+        <v>61.56773376464844</v>
       </c>
       <c r="C85" t="n">
         <v>73.90814208984375</v>
@@ -2438,11 +2450,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>68.09904479980469</v>
+        <v>68.09900665283203</v>
       </c>
       <c r="C86" t="n">
         <v>81.74858856201172</v>
@@ -2467,11 +2479,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>70.77065277099609</v>
+        <v>70.77064514160156</v>
       </c>
       <c r="C87" t="n">
         <v>84.95568084716797</v>
@@ -2496,11 +2508,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>66.00297546386719</v>
+        <v>66.00299072265625</v>
       </c>
       <c r="C88" t="n">
         <v>79.12973022460938</v>
@@ -2525,11 +2537,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>63.18676376342773</v>
+        <v>63.186767578125</v>
       </c>
       <c r="C89" t="n">
         <v>75.75342559814453</v>
@@ -2554,11 +2566,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>64.75283050537109</v>
+        <v>64.75283813476562</v>
       </c>
       <c r="C90" t="n">
         <v>77.63094329833984</v>
@@ -2583,7 +2595,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2612,11 +2624,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>71.35536193847656</v>
+        <v>71.35539245605469</v>
       </c>
       <c r="C92" t="n">
         <v>85.41498565673828</v>
@@ -2641,11 +2653,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>72.2708740234375</v>
+        <v>72.27088165283203</v>
       </c>
       <c r="C93" t="n">
         <v>86.51087951660156</v>
@@ -2670,11 +2682,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>76.92051696777344</v>
+        <v>76.9205322265625</v>
       </c>
       <c r="C94" t="n">
         <v>91.95004272460938</v>
@@ -2699,7 +2711,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2728,11 +2740,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>93.4964599609375</v>
+        <v>93.49645233154297</v>
       </c>
       <c r="C96" t="n">
         <v>111.7647094726562</v>
@@ -2757,11 +2769,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>97.01818084716797</v>
+        <v>97.01817321777344</v>
       </c>
       <c r="C97" t="n">
         <v>115.8501205444336</v>
@@ -2786,11 +2798,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>89.96635437011719</v>
+        <v>89.96633148193359</v>
       </c>
       <c r="C98" t="n">
         <v>107.4294891357422</v>
@@ -2815,7 +2827,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2844,11 +2856,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>89.55133819580078</v>
+        <v>89.55132293701172</v>
       </c>
       <c r="C100" t="n">
         <v>106.8170852661133</v>
@@ -2873,11 +2885,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>92.04412078857422</v>
+        <v>92.04409790039062</v>
       </c>
       <c r="C101" t="n">
         <v>109.7904891967773</v>
@@ -2902,11 +2914,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>97.38774108886719</v>
+        <v>97.38776397705078</v>
       </c>
       <c r="C102" t="n">
         <v>116.1643829345703</v>
@@ -2931,11 +2943,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>102.4121246337891</v>
+        <v>102.4121170043945</v>
       </c>
       <c r="C103" t="n">
         <v>121.9822692871094</v>
@@ -2960,11 +2972,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>99.36776733398438</v>
+        <v>99.36775207519531</v>
       </c>
       <c r="C104" t="n">
         <v>118.3561630249023</v>
@@ -2989,11 +3001,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>100.0442810058594</v>
+        <v>100.044319152832</v>
       </c>
       <c r="C105" t="n">
         <v>119.1619644165039</v>
@@ -3018,11 +3030,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>109.3673934936523</v>
+        <v>109.3673858642578</v>
       </c>
       <c r="C106" t="n">
         <v>130.0966949462891</v>
@@ -3047,11 +3059,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>113.3980026245117</v>
+        <v>113.3979415893555</v>
       </c>
       <c r="C107" t="n">
         <v>134.8912200927734</v>
@@ -3076,11 +3088,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>120.7004470825195</v>
+        <v>120.7004318237305</v>
       </c>
       <c r="C108" t="n">
         <v>143.5777587890625</v>
@@ -3105,7 +3117,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3134,11 +3146,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>114.6846542358398</v>
+        <v>114.6846466064453</v>
       </c>
       <c r="C110" t="n">
         <v>136.2691345214844</v>
@@ -3163,11 +3175,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>120.021858215332</v>
+        <v>120.0218048095703</v>
       </c>
       <c r="C111" t="n">
         <v>142.6107940673828</v>
@@ -3192,11 +3204,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>112.3322601318359</v>
+        <v>112.3322677612305</v>
       </c>
       <c r="C112" t="n">
         <v>133.3199005126953</v>
@@ -3221,11 +3233,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>115.1295547485352</v>
+        <v>115.1295700073242</v>
       </c>
       <c r="C113" t="n">
         <v>136.6398010253906</v>
@@ -3250,7 +3262,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3279,11 +3291,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>115.8516159057617</v>
+        <v>115.8516387939453</v>
       </c>
       <c r="C115" t="n">
         <v>137.3086242675781</v>
@@ -3308,11 +3320,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>116.5451507568359</v>
+        <v>116.5450744628906</v>
       </c>
       <c r="C116" t="n">
         <v>138.1305389404297</v>
@@ -3337,11 +3349,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>102.3967895507812</v>
+        <v>102.3968048095703</v>
       </c>
       <c r="C117" t="n">
         <v>121.3618087768555</v>
@@ -3366,11 +3378,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>98.05416870117188</v>
+        <v>98.05413055419922</v>
       </c>
       <c r="C118" t="n">
         <v>116.0193405151367</v>
@@ -3395,11 +3407,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>106.2741165161133</v>
+        <v>106.2741394042969</v>
       </c>
       <c r="C119" t="n">
         <v>125.7453689575195</v>
@@ -3424,11 +3436,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>107.9698715209961</v>
+        <v>107.9698638916016</v>
       </c>
       <c r="C120" t="n">
         <v>127.7518157958984</v>
@@ -3453,11 +3465,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>101.6388702392578</v>
+        <v>101.6388854980469</v>
       </c>
       <c r="C121" t="n">
         <v>120.0564041137695</v>
@@ -3482,11 +3494,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>90.64888000488281</v>
+        <v>90.64887237548828</v>
       </c>
       <c r="C122" t="n">
         <v>107.0749435424805</v>
@@ -3511,11 +3523,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>93.37761688232422</v>
+        <v>93.37762451171875</v>
       </c>
       <c r="C123" t="n">
         <v>110.2981491088867</v>
@@ -3540,11 +3552,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>111.2010879516602</v>
+        <v>111.2011260986328</v>
       </c>
       <c r="C124" t="n">
         <v>131.1200714111328</v>
@@ -3569,11 +3581,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>112.8344268798828</v>
+        <v>112.8344116210938</v>
       </c>
       <c r="C125" t="n">
         <v>133.0459289550781</v>
@@ -3598,11 +3610,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>112.7387161254883</v>
+        <v>112.7387084960938</v>
       </c>
       <c r="C126" t="n">
         <v>132.9331207275391</v>
@@ -3627,11 +3639,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>103.9840850830078</v>
+        <v>103.9840774536133</v>
       </c>
       <c r="C127" t="n">
         <v>122.3045959472656</v>
@@ -3656,11 +3668,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>110.9172592163086</v>
+        <v>110.9172821044922</v>
       </c>
       <c r="C128" t="n">
         <v>130.4593048095703</v>
@@ -3685,11 +3697,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>112.9931106567383</v>
+        <v>112.9930801391602</v>
       </c>
       <c r="C129" t="n">
         <v>132.90087890625</v>
@@ -3714,11 +3726,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>119.9632949829102</v>
+        <v>119.9632797241211</v>
       </c>
       <c r="C130" t="n">
         <v>140.7574615478516</v>
@@ -3743,11 +3755,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>119.7160873413086</v>
+        <v>119.7160491943359</v>
       </c>
       <c r="C131" t="n">
         <v>140.4673614501953</v>
@@ -3772,11 +3784,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>131.63134765625</v>
+        <v>131.6313323974609</v>
       </c>
       <c r="C132" t="n">
         <v>154.4480285644531</v>
@@ -3801,11 +3813,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>128.1355438232422</v>
+        <v>128.1355895996094</v>
       </c>
       <c r="C133" t="n">
         <v>150.040283203125</v>
@@ -3830,11 +3842,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>130.1381072998047</v>
+        <v>130.1381225585938</v>
       </c>
       <c r="C134" t="n">
         <v>152.3851776123047</v>
@@ -3859,11 +3871,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>132.8012847900391</v>
+        <v>132.8013153076172</v>
       </c>
       <c r="C135" t="n">
         <v>155.5036315917969</v>
@@ -3888,11 +3900,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>134.5736389160156</v>
+        <v>134.5736694335938</v>
       </c>
       <c r="C136" t="n">
         <v>157.2522125244141</v>
@@ -3917,11 +3929,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>130.8153839111328</v>
+        <v>130.8153533935547</v>
       </c>
       <c r="C137" t="n">
         <v>152.860595703125</v>
@@ -3946,11 +3958,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>133.6703033447266</v>
+        <v>133.6702575683594</v>
       </c>
       <c r="C138" t="n">
         <v>156.1966094970703</v>
@@ -3975,11 +3987,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>150.2248077392578</v>
+        <v>150.2248687744141</v>
       </c>
       <c r="C139" t="n">
         <v>175.1248931884766</v>
@@ -4004,11 +4016,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>143.7964324951172</v>
+        <v>143.7963562011719</v>
       </c>
       <c r="C140" t="n">
         <v>167.6309356689453</v>
@@ -4033,7 +4045,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4062,11 +4074,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>156.2931976318359</v>
+        <v>156.2931671142578</v>
       </c>
       <c r="C142" t="n">
         <v>181.7727661132812</v>
@@ -4091,11 +4103,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>156.4525604248047</v>
+        <v>156.4525756835938</v>
       </c>
       <c r="C143" t="n">
         <v>181.9580993652344</v>
@@ -4120,11 +4132,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>160.3671722412109</v>
+        <v>160.3672027587891</v>
       </c>
       <c r="C144" t="n">
         <v>186.5108795166016</v>
@@ -4149,7 +4161,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4178,11 +4190,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>182.2402038574219</v>
+        <v>182.2401428222656</v>
       </c>
       <c r="C146" t="n">
         <v>211.5068511962891</v>
@@ -4207,11 +4219,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>171.0827484130859</v>
+        <v>171.0827789306641</v>
       </c>
       <c r="C147" t="n">
         <v>198.5576171875</v>
@@ -4236,11 +4248,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>167.0560302734375</v>
+        <v>167.0560455322266</v>
       </c>
       <c r="C148" t="n">
         <v>193.4810638427734</v>
@@ -4265,7 +4277,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4294,11 +4306,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>173.3246917724609</v>
+        <v>173.3246765136719</v>
       </c>
       <c r="C150" t="n">
         <v>200.7413330078125</v>
@@ -4323,7 +4335,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4352,7 +4364,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4381,11 +4393,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>170.1760559082031</v>
+        <v>170.1760406494141</v>
       </c>
       <c r="C153" t="n">
         <v>196.5753479003906</v>
@@ -4410,11 +4422,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>168.4163208007812</v>
+        <v>168.4162750244141</v>
       </c>
       <c r="C154" t="n">
         <v>194.0290069580078</v>
@@ -4439,11 +4451,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>154.1129150390625</v>
+        <v>154.1129455566406</v>
       </c>
       <c r="C155" t="n">
         <v>177.5503692626953</v>
@@ -4468,11 +4480,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>160.1700286865234</v>
+        <v>160.1700439453125</v>
       </c>
       <c r="C156" t="n">
         <v>184.5286102294922</v>
@@ -4497,11 +4509,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>113.181510925293</v>
+        <v>113.1815032958984</v>
       </c>
       <c r="C157" t="n">
         <v>130</v>
@@ -4526,11 +4538,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>124.5747604370117</v>
+        <v>124.5747451782227</v>
       </c>
       <c r="C158" t="n">
         <v>143.0862274169922</v>
@@ -4555,7 +4567,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4584,11 +4596,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>127.7490997314453</v>
+        <v>127.7490539550781</v>
       </c>
       <c r="C160" t="n">
         <v>146.1804962158203</v>
@@ -4613,11 +4625,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>133.4178314208984</v>
+        <v>133.4178771972656</v>
       </c>
       <c r="C161" t="n">
         <v>152.6672058105469</v>
@@ -4642,11 +4654,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>108.6440887451172</v>
+        <v>108.6440963745117</v>
       </c>
       <c r="C162" t="n">
         <v>124.3190994262695</v>
@@ -4671,11 +4683,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>116.0705108642578</v>
+        <v>116.0704650878906</v>
       </c>
       <c r="C163" t="n">
         <v>132.3045959472656</v>
@@ -4700,11 +4712,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>120.552375793457</v>
+        <v>120.5523910522461</v>
       </c>
       <c r="C164" t="n">
         <v>137.4133758544922</v>
@@ -4729,11 +4741,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>112.1258163452148</v>
+        <v>112.1258239746094</v>
       </c>
       <c r="C165" t="n">
         <v>127.808219909668</v>
@@ -4758,11 +4770,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>103.3160247802734</v>
+        <v>103.3160171508789</v>
       </c>
       <c r="C166" t="n">
         <v>117.3005676269531</v>
@@ -4787,11 +4799,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>108.3480377197266</v>
+        <v>108.3480453491211</v>
       </c>
       <c r="C167" t="n">
         <v>123.0137023925781</v>
@@ -4816,11 +4828,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>113.5929641723633</v>
+        <v>113.5929718017578</v>
       </c>
       <c r="C168" t="n">
         <v>128.9685668945312</v>
@@ -4845,7 +4857,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4874,11 +4886,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>103.0912704467773</v>
+        <v>103.0912475585938</v>
       </c>
       <c r="C170" t="n">
         <v>116.5511703491211</v>
@@ -4903,11 +4915,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>100.6180114746094</v>
+        <v>100.6180191040039</v>
       </c>
       <c r="C171" t="n">
         <v>113.7550354003906</v>
@@ -4932,11 +4944,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>86.86185455322266</v>
+        <v>86.86184692382812</v>
       </c>
       <c r="C172" t="n">
         <v>97.71152496337891</v>
@@ -4959,11 +4971,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>90.80880737304688</v>
+        <v>90.80882263183594</v>
       </c>
       <c r="C173" t="n">
         <v>102.1514892578125</v>
@@ -4986,11 +4998,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>93.52368927001953</v>
+        <v>93.52369689941406</v>
       </c>
       <c r="C174" t="n">
         <v>105.2054824829102</v>
@@ -5013,7 +5025,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5040,7 +5052,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5069,7 +5081,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5098,11 +5110,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>181.552978515625</v>
+        <v>181.5529479980469</v>
       </c>
       <c r="C178" t="n">
         <v>202.6752624511719</v>
@@ -5127,11 +5139,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>187.2914428710938</v>
+        <v>187.2914276123047</v>
       </c>
       <c r="C179" t="n">
         <v>209.0813903808594</v>
@@ -5156,11 +5168,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>206.8600311279297</v>
+        <v>206.8600921630859</v>
       </c>
       <c r="C180" t="n">
         <v>230.9266662597656</v>
@@ -5185,7 +5197,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5214,11 +5226,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>170.2542572021484</v>
+        <v>170.2542877197266</v>
       </c>
       <c r="C182" t="n">
         <v>189.6373901367188</v>
@@ -5243,11 +5255,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>184.1154022216797</v>
+        <v>184.1154327392578</v>
       </c>
       <c r="C183" t="n">
         <v>205.0765533447266</v>
@@ -5272,11 +5284,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>206.0208129882812</v>
+        <v>206.0207977294922</v>
       </c>
       <c r="C184" t="n">
         <v>228.8799285888672</v>
@@ -5301,11 +5313,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>210.5685729980469</v>
+        <v>210.5685577392578</v>
       </c>
       <c r="C185" t="n">
         <v>233.9323120117188</v>
@@ -5330,7 +5342,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5359,11 +5371,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>216.9214019775391</v>
+        <v>216.9213714599609</v>
       </c>
       <c r="C187" t="n">
         <v>240.3948364257812</v>
@@ -5388,11 +5400,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>203.5569458007812</v>
+        <v>203.5569305419922</v>
       </c>
       <c r="C188" t="n">
         <v>225.5842132568359</v>
@@ -5417,7 +5429,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5446,11 +5458,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>159.9008941650391</v>
+        <v>159.90087890625</v>
       </c>
       <c r="C190" t="n">
         <v>176.7042694091797</v>
@@ -5475,11 +5487,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>171.7426910400391</v>
+        <v>171.74267578125</v>
       </c>
       <c r="C191" t="n">
         <v>189.7904968261719</v>
@@ -5504,7 +5516,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5533,11 +5545,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>189.1724548339844</v>
+        <v>189.1724395751953</v>
       </c>
       <c r="C193" t="n">
         <v>208.4125671386719</v>
@@ -5562,11 +5574,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>179.8249816894531</v>
+        <v>179.8250122070312</v>
       </c>
       <c r="C194" t="n">
         <v>198.1144256591797</v>
@@ -5591,7 +5603,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5620,7 +5632,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5649,11 +5661,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>145.8551483154297</v>
+        <v>145.8551177978516</v>
       </c>
       <c r="C197" t="n">
         <v>160.1450500488281</v>
@@ -5678,11 +5690,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>164.8190765380859</v>
+        <v>164.819091796875</v>
       </c>
       <c r="C198" t="n">
         <v>180.9669647216797</v>
@@ -5707,11 +5719,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>167.2252502441406</v>
+        <v>167.2252655029297</v>
       </c>
       <c r="C199" t="n">
         <v>182.6833190917969</v>
@@ -5736,11 +5748,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>171.9312744140625</v>
+        <v>171.9313049316406</v>
       </c>
       <c r="C200" t="n">
         <v>187.8243408203125</v>
@@ -5765,11 +5777,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>155.4971771240234</v>
+        <v>155.4971466064453</v>
       </c>
       <c r="C201" t="n">
         <v>169.8710784912109</v>
@@ -5794,7 +5806,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5823,11 +5835,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>118.8738174438477</v>
+        <v>118.8738098144531</v>
       </c>
       <c r="C203" t="n">
         <v>129.1539154052734</v>
@@ -5852,11 +5864,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>135.1459045410156</v>
+        <v>135.1459503173828</v>
       </c>
       <c r="C204" t="n">
         <v>146.8332061767578</v>
@@ -5881,11 +5893,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>129.3212127685547</v>
+        <v>129.3211975097656</v>
       </c>
       <c r="C205" t="n">
         <v>139.5648651123047</v>
@@ -5910,11 +5922,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>144.7471771240234</v>
+        <v>144.7471466064453</v>
       </c>
       <c r="C206" t="n">
         <v>156.2127380371094</v>
@@ -5939,7 +5951,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5968,7 +5980,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5997,7 +6009,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6026,11 +6038,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>163.6621551513672</v>
+        <v>163.6621856689453</v>
       </c>
       <c r="C210" t="n">
         <v>175.6486663818359</v>
@@ -6055,11 +6067,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>187.1746063232422</v>
+        <v>187.1745910644531</v>
       </c>
       <c r="C211" t="n">
         <v>199.7582550048828</v>
@@ -6084,11 +6096,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>203.8233032226562</v>
+        <v>203.8232727050781</v>
       </c>
       <c r="C212" t="n">
         <v>217.5261840820312</v>
@@ -6113,11 +6125,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>197.0807647705078</v>
+        <v>197.0807342529297</v>
       </c>
       <c r="C213" t="n">
         <v>210.3303833007812</v>
@@ -6142,7 +6154,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6171,11 +6183,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>182.1814117431641</v>
+        <v>182.1814422607422</v>
       </c>
       <c r="C215" t="n">
         <v>193.4730072021484</v>
@@ -6200,11 +6212,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>196.3932647705078</v>
+        <v>196.3932495117188</v>
       </c>
       <c r="C216" t="n">
         <v>208.565673828125</v>
@@ -6229,11 +6241,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>192.8547668457031</v>
+        <v>192.8547821044922</v>
       </c>
       <c r="C217" t="n">
         <v>203.8436737060547</v>
@@ -6258,11 +6270,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>183.9504241943359</v>
+        <v>183.9504089355469</v>
       </c>
       <c r="C218" t="n">
         <v>194.4319152832031</v>
@@ -6287,7 +6299,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6316,11 +6328,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>222.0046691894531</v>
+        <v>222.0046997070312</v>
       </c>
       <c r="C220" t="n">
         <v>233.4730072021484</v>
@@ -6345,11 +6357,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>200.5811462402344</v>
+        <v>200.5811614990234</v>
       </c>
       <c r="C221" t="n">
         <v>210.9427947998047</v>
@@ -6374,11 +6386,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>194.58935546875</v>
+        <v>194.5893249511719</v>
       </c>
       <c r="C222" t="n">
         <v>204.6414184570312</v>
@@ -6403,11 +6415,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>231.0002288818359</v>
+        <v>231.000244140625</v>
       </c>
       <c r="C223" t="n">
         <v>241.6116027832031</v>
@@ -6432,11 +6444,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>232.8569183349609</v>
+        <v>232.8569488525391</v>
       </c>
       <c r="C224" t="n">
         <v>243.5535888671875</v>
@@ -6461,11 +6473,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>230.1758880615234</v>
+        <v>230.1758575439453</v>
       </c>
       <c r="C225" t="n">
         <v>240.7493896484375</v>
@@ -6490,11 +6502,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>211.8792877197266</v>
+        <v>211.8793029785156</v>
       </c>
       <c r="C226" t="n">
         <v>220.5318298339844</v>
@@ -6519,11 +6531,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>212.0109100341797</v>
+        <v>212.0109252929688</v>
       </c>
       <c r="C227" t="n">
         <v>220.6688079833984</v>
@@ -6548,11 +6560,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>234.3229827880859</v>
+        <v>234.3229675292969</v>
       </c>
       <c r="C228" t="n">
         <v>243.8920288085938</v>
@@ -6577,7 +6589,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6606,11 +6618,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>206.0718994140625</v>
+        <v>206.0718841552734</v>
       </c>
       <c r="C230" t="n">
         <v>213.4327087402344</v>
@@ -6635,11 +6647,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>204.5392456054688</v>
+        <v>204.5392303466797</v>
       </c>
       <c r="C231" t="n">
         <v>211.8452911376953</v>
@@ -6664,7 +6676,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6693,7 +6705,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6722,11 +6734,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>170.6115112304688</v>
+        <v>170.6115417480469</v>
       </c>
       <c r="C234" t="n">
         <v>175.745361328125</v>
@@ -6751,7 +6763,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6780,11 +6792,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>175.9566497802734</v>
+        <v>175.9566650390625</v>
       </c>
       <c r="C236" t="n">
         <v>180.0886383056641</v>
@@ -6809,11 +6821,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>181.9244842529297</v>
+        <v>181.9244689941406</v>
       </c>
       <c r="C237" t="n">
         <v>186.1966094970703</v>
@@ -6838,7 +6850,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6867,7 +6879,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6896,11 +6908,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>218.4374084472656</v>
+        <v>218.4374237060547</v>
       </c>
       <c r="C240" t="n">
         <v>222.1434326171875</v>
@@ -6925,11 +6937,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>230.0538940429688</v>
+        <v>230.0538787841797</v>
       </c>
       <c r="C241" t="n">
         <v>232.7639007568359</v>
@@ -6954,7 +6966,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6983,7 +6995,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7012,7 +7024,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7041,11 +7053,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>322.5063781738281</v>
+        <v>322.5064086914062</v>
       </c>
       <c r="C245" t="n">
         <v>324.9879150390625</v>
@@ -7070,7 +7082,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7099,7 +7111,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7128,7 +7140,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7157,7 +7169,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7186,32 +7198,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>291.5</v>
+        <v>279.5400085449219</v>
       </c>
       <c r="C250" t="n">
-        <v>291.5</v>
+        <v>279.5400085449219</v>
       </c>
       <c r="D250" t="n">
-        <v>26031400</v>
+        <v>28605900</v>
       </c>
       <c r="E250" t="n">
         <v>18.55</v>
       </c>
       <c r="F250" t="n">
-        <v>15.71428571428571</v>
+        <v>15.06954223961843</v>
       </c>
       <c r="G250" t="n">
         <v>236581188</v>
       </c>
       <c r="H250" t="n">
-        <v>68963416302</v>
+        <v>66133907315.08777</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1100315719101047</v>
+        <v>0.120913671293256</v>
       </c>
     </row>
   </sheetData>
@@ -7243,75 +7255,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39600</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39691</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40074</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7347,13 +7359,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39692</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39782</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40165</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7389,13 +7401,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39783</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39872</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40256</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7431,13 +7443,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39873</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39964</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40374</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7464,7 +7476,7 @@
       <c r="I5" t="n">
         <v>0.2497985495568091</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40374</v>
       </c>
       <c r="K5" t="n">
@@ -7477,13 +7489,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39965</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40056</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40074</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7510,7 +7522,7 @@
       <c r="I6" t="n">
         <v>-0.2739726027397258</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40374</v>
       </c>
       <c r="K6" t="n">
@@ -7523,13 +7535,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40057</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40147</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40165</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7556,7 +7568,7 @@
       <c r="I7" t="n">
         <v>-0.6607574536663978</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40374</v>
       </c>
       <c r="K7" t="n">
@@ -7569,13 +7581,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40148</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40237</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40256</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7602,7 +7614,7 @@
       <c r="I8" t="n">
         <v>-0.2981466559226428</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40374</v>
       </c>
       <c r="K8" t="n">
@@ -7615,13 +7627,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40238</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40329</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40374</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7648,7 +7660,7 @@
       <c r="I9" t="n">
         <v>3.029814665592264</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40374</v>
       </c>
       <c r="K9" t="n">
@@ -7661,13 +7673,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40330</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40421</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40438</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7694,7 +7706,7 @@
       <c r="I10" t="n">
         <v>3.529411764705882</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40438</v>
       </c>
       <c r="K10" t="n">
@@ -7707,13 +7719,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40422</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40512</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7740,7 +7752,7 @@
       <c r="I11" t="n">
         <v>3.360193392425463</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="K11" t="n">
@@ -7753,13 +7765,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40513</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40602</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40620</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7786,7 +7798,7 @@
       <c r="I12" t="n">
         <v>3.336019339242546</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40620</v>
       </c>
       <c r="K12" t="n">
@@ -7799,13 +7811,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40603</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40694</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40736</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7832,7 +7844,7 @@
       <c r="I13" t="n">
         <v>3.682514101531023</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40736</v>
       </c>
       <c r="K13" t="n">
@@ -7845,13 +7857,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40695</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40786</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40809</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7878,7 +7890,7 @@
       <c r="I14" t="n">
         <v>3.892022562449637</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40809</v>
       </c>
       <c r="K14" t="n">
@@ -7891,13 +7903,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40787</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40877</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40893</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7924,7 +7936,7 @@
       <c r="I15" t="n">
         <v>4.439967767929089</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40893</v>
       </c>
       <c r="K15" t="n">
@@ -7937,13 +7949,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40878</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40968</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>40991</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7970,7 +7982,7 @@
       <c r="I16" t="n">
         <v>5.181305398871877</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>40991</v>
       </c>
       <c r="K16" t="n">
@@ -7983,13 +7995,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40969</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41060</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41106</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8016,7 +8028,7 @@
       <c r="I17" t="n">
         <v>5.165189363416599</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41106</v>
       </c>
       <c r="K17" t="n">
@@ -8029,13 +8041,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41061</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41152</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41171</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8062,7 +8074,7 @@
       <c r="I18" t="n">
         <v>5.15713134568896</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41171</v>
       </c>
       <c r="K18" t="n">
@@ -8075,13 +8087,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41153</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41263</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8108,7 +8120,7 @@
       <c r="I19" t="n">
         <v>5.012087026591458</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41263</v>
       </c>
       <c r="K19" t="n">
@@ -8121,13 +8133,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41244</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41333</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41354</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8154,7 +8166,7 @@
       <c r="I20" t="n">
         <v>4.593070104754229</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41354</v>
       </c>
       <c r="K20" t="n">
@@ -8167,13 +8179,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41334</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41425</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41470</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8200,7 +8212,7 @@
       <c r="I21" t="n">
         <v>3.964544721998388</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41470</v>
       </c>
       <c r="K21" t="n">
@@ -8213,13 +8225,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41426</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41517</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41536</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8246,7 +8258,7 @@
       <c r="I22" t="n">
         <v>4.0290088638195</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41536</v>
       </c>
       <c r="K22" t="n">
@@ -8259,13 +8271,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41518</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41608</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41627</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8292,7 +8304,7 @@
       <c r="I23" t="n">
         <v>4.174053182917001</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41627</v>
       </c>
       <c r="K23" t="n">
@@ -8305,13 +8317,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41609</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41698</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41718</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8338,7 +8350,7 @@
       <c r="I24" t="n">
         <v>4.254633360193392</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41718</v>
       </c>
       <c r="K24" t="n">
@@ -8351,13 +8363,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41699</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41790</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41834</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8384,7 +8396,7 @@
       <c r="I25" t="n">
         <v>5.471394037066881</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41834</v>
       </c>
       <c r="K25" t="n">
@@ -8397,13 +8409,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41791</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41882</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41900</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8430,7 +8442,7 @@
       <c r="I26" t="n">
         <v>5.930701047542304</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41900</v>
       </c>
       <c r="K26" t="n">
@@ -8443,13 +8455,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41883</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41973</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>41991</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8476,7 +8488,7 @@
       <c r="I27" t="n">
         <v>6.390008058017727</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>41991</v>
       </c>
       <c r="K27" t="n">
@@ -8489,13 +8501,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41974</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42063</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42082</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8522,7 +8534,7 @@
       <c r="I28" t="n">
         <v>7.018533440773568</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42082</v>
       </c>
       <c r="K28" t="n">
@@ -8535,13 +8547,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42064</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42155</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42199</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8568,7 +8580,7 @@
       <c r="I29" t="n">
         <v>2.489927477840451</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42199</v>
       </c>
       <c r="K29" t="n">
@@ -8581,13 +8593,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42156</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42247</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42264</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8614,7 +8626,7 @@
       <c r="I30" t="n">
         <v>2.747784045124899</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42264</v>
       </c>
       <c r="K30" t="n">
@@ -8627,13 +8639,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42248</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42338</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42355</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8660,7 +8672,7 @@
       <c r="I31" t="n">
         <v>2.989524576954069</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42355</v>
       </c>
       <c r="K31" t="n">
@@ -8673,13 +8685,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42339</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42429</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42446</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8706,7 +8718,7 @@
       <c r="I32" t="n">
         <v>2.852538275584206</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42446</v>
       </c>
       <c r="K32" t="n">
@@ -8719,13 +8731,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42430</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42521</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42569</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8752,7 +8764,7 @@
       <c r="I33" t="n">
         <v>5.189363416599517</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42569</v>
       </c>
       <c r="K33" t="n">
@@ -8765,13 +8777,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42522</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42613</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42634</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8798,7 +8810,7 @@
       <c r="I34" t="n">
         <v>5.374697824335213</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42634</v>
       </c>
       <c r="K34" t="n">
@@ -8811,13 +8823,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42614</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42704</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42725</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8844,7 +8856,7 @@
       <c r="I35" t="n">
         <v>5.495568090249798</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42725</v>
       </c>
       <c r="K35" t="n">
@@ -8857,13 +8869,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42705</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42794</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42816</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8890,7 +8902,7 @@
       <c r="I36" t="n">
         <v>5.680902497985495</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42816</v>
       </c>
       <c r="K36" t="n">
@@ -8903,13 +8915,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42795</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42886</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42933</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8936,7 +8948,7 @@
       <c r="I37" t="n">
         <v>8.912167606768733</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42933</v>
       </c>
       <c r="K37" t="n">
@@ -8949,13 +8961,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42887</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42978</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>42998</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8982,7 +8994,7 @@
       <c r="I38" t="n">
         <v>8.541498791297339</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>42998</v>
       </c>
       <c r="K38" t="n">
@@ -8995,13 +9007,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42979</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43069</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43089</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9028,7 +9040,7 @@
       <c r="I39" t="n">
         <v>8.742949234488314</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43089</v>
       </c>
       <c r="K39" t="n">
@@ -9041,13 +9053,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43070</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43159</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43180</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9074,7 +9086,7 @@
       <c r="I40" t="n">
         <v>13.19097502014504</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43180</v>
       </c>
       <c r="K40" t="n">
@@ -9087,13 +9099,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43160</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43251</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43297</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9120,7 +9132,7 @@
       <c r="I41" t="n">
         <v>13.5132957292506</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43297</v>
       </c>
       <c r="K41" t="n">
@@ -9133,13 +9145,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43252</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43343</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43360</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9166,7 +9178,7 @@
       <c r="I42" t="n">
         <v>14.24657534246575</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43360</v>
       </c>
       <c r="K42" t="n">
@@ -9179,13 +9191,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43344</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43434</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43452</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9212,7 +9224,7 @@
       <c r="I43" t="n">
         <v>14.78646253021756</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43452</v>
       </c>
       <c r="K43" t="n">
@@ -9225,13 +9237,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43435</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43524</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43543</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9258,7 +9270,7 @@
       <c r="I44" t="n">
         <v>10.92667203867848</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43543</v>
       </c>
       <c r="K44" t="n">
@@ -9271,13 +9283,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43525</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43616</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43662</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9304,7 +9316,7 @@
       <c r="I45" t="n">
         <v>1.490733279613215</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43662</v>
       </c>
       <c r="K45" t="n">
@@ -9317,13 +9329,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43617</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43708</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43725</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9350,7 +9362,7 @@
       <c r="I46" t="n">
         <v>1.281224818694601</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43725</v>
       </c>
       <c r="K46" t="n">
@@ -9363,13 +9375,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43709</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43799</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43816</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9396,7 +9408,7 @@
       <c r="I47" t="n">
         <v>0.1692183722804188</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43816</v>
       </c>
       <c r="K47" t="n">
@@ -9409,13 +9421,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43800</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43890</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43907</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9442,7 +9454,7 @@
       <c r="I48" t="n">
         <v>-1.120064464141821</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43907</v>
       </c>
       <c r="K48" t="n">
@@ -9455,13 +9467,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43891</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43982</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44032</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9488,7 +9500,7 @@
       <c r="I49" t="n">
         <v>3.940370668815471</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44032</v>
       </c>
       <c r="K49" t="n">
@@ -9501,13 +9513,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43983</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44074</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44089</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9534,7 +9546,7 @@
       <c r="I50" t="n">
         <v>5.455278001611603</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44089</v>
       </c>
       <c r="K50" t="n">
@@ -9547,13 +9559,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44075</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44165</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44182</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9580,7 +9592,7 @@
       <c r="I51" t="n">
         <v>7.40531829170024</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44182</v>
       </c>
       <c r="K51" t="n">
@@ -9593,13 +9605,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44166</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44255</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44273</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9626,7 +9638,7 @@
       <c r="I52" t="n">
         <v>9.09750201450443</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44273</v>
       </c>
       <c r="K52" t="n">
@@ -9639,13 +9651,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44256</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44347</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44396</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9672,7 +9684,7 @@
       <c r="I53" t="n">
         <v>15.67284448025785</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44396</v>
       </c>
       <c r="K53" t="n">
@@ -9685,13 +9697,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44348</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44439</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44460</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9718,7 +9730,7 @@
       <c r="I54" t="n">
         <v>15.1651893634166</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44460</v>
       </c>
       <c r="K54" t="n">
@@ -9731,13 +9743,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44440</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44530</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44546</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9764,7 +9776,7 @@
       <c r="I55" t="n">
         <v>14.62530217566478</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44546</v>
       </c>
       <c r="K55" t="n">
@@ -9777,13 +9789,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44531</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44620</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44637</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9810,7 +9822,7 @@
       <c r="I56" t="n">
         <v>15.35052377115229</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44637</v>
       </c>
       <c r="K56" t="n">
@@ -9823,13 +9835,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44621</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44712</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44760</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9856,7 +9868,7 @@
       <c r="I57" t="n">
         <v>11.54713940370669</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44760</v>
       </c>
       <c r="K57" t="n">
@@ -9869,13 +9881,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44713</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44804</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44826</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9902,7 +9914,7 @@
       <c r="I58" t="n">
         <v>10.93473005640612</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44826</v>
       </c>
       <c r="K58" t="n">
@@ -9915,13 +9927,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44805</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44895</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44915</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9948,7 +9960,7 @@
       <c r="I59" t="n">
         <v>10.28203062046736</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44915</v>
       </c>
       <c r="K59" t="n">
@@ -9961,13 +9973,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44896</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44985</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45001</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9994,7 +10006,7 @@
       <c r="I60" t="n">
         <v>9.355358581788879</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45001</v>
       </c>
       <c r="K60" t="n">
@@ -10007,13 +10019,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44986</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45077</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45124</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10040,7 +10052,7 @@
       <c r="I61" t="n">
         <v>12.47381144238517</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45124</v>
       </c>
       <c r="K61" t="n">
@@ -10053,13 +10065,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45078</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45169</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45189</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10086,7 +10098,7 @@
       <c r="I62" t="n">
         <v>13.19903303787268</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45189</v>
       </c>
       <c r="K62" t="n">
@@ -10099,13 +10111,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45170</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45260</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45279</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10132,7 +10144,7 @@
       <c r="I63" t="n">
         <v>13.58581788879935</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45279</v>
       </c>
       <c r="K63" t="n">
@@ -10145,13 +10157,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45261</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45351</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45372</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10178,7 +10190,7 @@
       <c r="I64" t="n">
         <v>13.95648670427075</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45372</v>
       </c>
       <c r="K64" t="n">
@@ -10191,13 +10203,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45352</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45443</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45488</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10224,7 +10236,7 @@
       <c r="I65" t="n">
         <v>13.86784850926672</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45488</v>
       </c>
       <c r="K65" t="n">
@@ -10237,13 +10249,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45444</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45535</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45554</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10270,7 +10282,7 @@
       <c r="I66" t="n">
         <v>13.04593070104754</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45554</v>
       </c>
       <c r="K66" t="n">
@@ -10283,13 +10295,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45536</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45626</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10316,7 +10328,7 @@
       <c r="I67" t="n">
         <v>12.62691377921031</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="K67" t="n">
@@ -10329,13 +10341,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45627</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45716</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10362,7 +10374,7 @@
       <c r="I68" t="n">
         <v>12.82836422240129</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="K68" t="n">
@@ -10375,13 +10387,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45717</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45808</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10408,7 +10420,7 @@
       <c r="I69" t="n">
         <v>13.54552780016116</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="K69" t="n">
@@ -10421,13 +10433,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45809</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45918</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10454,7 +10466,7 @@
       <c r="I70" t="n">
         <v>13.74697824335214</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45918</v>
       </c>
       <c r="K70" t="n">
@@ -10467,13 +10479,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10500,7 +10512,7 @@
       <c r="I71" t="n">
         <v>14.56083803384367</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="K71" t="n">
@@ -10513,13 +10525,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46100</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10546,7 +10558,7 @@
       <c r="I72" t="n">
         <v>15.08460918614021</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46100</v>
       </c>
       <c r="K72" t="n">
@@ -10559,13 +10571,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46173</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46223</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10592,7 +10604,7 @@
       <c r="I73" t="n">
         <v>18.55</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46223</v>
       </c>
       <c r="K73" t="n">
@@ -10629,52 +10641,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40071</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40074</v>
       </c>
       <c r="C2" t="n">
@@ -10703,10 +10715,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40162</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40165</v>
       </c>
       <c r="C3" t="n">
@@ -10735,10 +10747,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40252</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40256</v>
       </c>
       <c r="C4" t="n">
@@ -10767,10 +10779,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40371</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40374</v>
       </c>
       <c r="C5" t="n">
@@ -10799,10 +10811,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40436</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40438</v>
       </c>
       <c r="C6" t="n">
@@ -10831,10 +10843,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40527</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="C7" t="n">
@@ -10863,10 +10875,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40618</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40620</v>
       </c>
       <c r="C8" t="n">
@@ -10895,10 +10907,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40735</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40736</v>
       </c>
       <c r="C9" t="n">
@@ -10927,10 +10939,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40807</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40809</v>
       </c>
       <c r="C10" t="n">
@@ -10959,10 +10971,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40891</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40893</v>
       </c>
       <c r="C11" t="n">
@@ -10991,10 +11003,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40989</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40991</v>
       </c>
       <c r="C12" t="n">
@@ -11023,10 +11035,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41103</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41106</v>
       </c>
       <c r="C13" t="n">
@@ -11055,10 +11067,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41169</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41171</v>
       </c>
       <c r="C14" t="n">
@@ -11087,10 +11099,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41261</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41263</v>
       </c>
       <c r="C15" t="n">
@@ -11119,10 +11131,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41352</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41354</v>
       </c>
       <c r="C16" t="n">
@@ -11151,10 +11163,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41467</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41470</v>
       </c>
       <c r="C17" t="n">
@@ -11183,10 +11195,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41535</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41536</v>
       </c>
       <c r="C18" t="n">
@@ -11215,10 +11227,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41626</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41627</v>
       </c>
       <c r="C19" t="n">
@@ -11247,10 +11259,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41717</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41718</v>
       </c>
       <c r="C20" t="n">
@@ -11279,10 +11291,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41831</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41834</v>
       </c>
       <c r="C21" t="n">
@@ -11311,10 +11323,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41899</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41900</v>
       </c>
       <c r="C22" t="n">
@@ -11343,10 +11355,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41990</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41991</v>
       </c>
       <c r="C23" t="n">
@@ -11375,10 +11387,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42081</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42082</v>
       </c>
       <c r="C24" t="n">
@@ -11407,10 +11419,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42195</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42199</v>
       </c>
       <c r="C25" t="n">
@@ -11439,10 +11451,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42263</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42264</v>
       </c>
       <c r="C26" t="n">
@@ -11471,10 +11483,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42353</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42355</v>
       </c>
       <c r="C27" t="n">
@@ -11503,10 +11515,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42445</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42446</v>
       </c>
       <c r="C28" t="n">
@@ -11535,10 +11547,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42565</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42569</v>
       </c>
       <c r="C29" t="n">
@@ -11567,10 +11579,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42633</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42634</v>
       </c>
       <c r="C30" t="n">
@@ -11599,10 +11611,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42724</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42725</v>
       </c>
       <c r="C31" t="n">
@@ -11631,10 +11643,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42814</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42816</v>
       </c>
       <c r="C32" t="n">
@@ -11663,10 +11675,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42929</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42933</v>
       </c>
       <c r="C33" t="n">
@@ -11695,10 +11707,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42996</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42998</v>
       </c>
       <c r="C34" t="n">
@@ -11727,10 +11739,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43087</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43089</v>
       </c>
       <c r="C35" t="n">
@@ -11759,10 +11771,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43178</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43180</v>
       </c>
       <c r="C36" t="n">
@@ -11791,10 +11803,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43293</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43297</v>
       </c>
       <c r="C37" t="n">
@@ -11823,10 +11835,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43356</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43360</v>
       </c>
       <c r="C38" t="n">
@@ -11855,10 +11867,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43448</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43452</v>
       </c>
       <c r="C39" t="n">
@@ -11887,10 +11899,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43539</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43543</v>
       </c>
       <c r="C40" t="n">
@@ -11919,10 +11931,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43658</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43662</v>
       </c>
       <c r="C41" t="n">
@@ -11951,10 +11963,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43721</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43725</v>
       </c>
       <c r="C42" t="n">
@@ -11983,10 +11995,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43812</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43816</v>
       </c>
       <c r="C43" t="n">
@@ -12015,10 +12027,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43903</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43907</v>
       </c>
       <c r="C44" t="n">
@@ -12047,10 +12059,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44028</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44032</v>
       </c>
       <c r="C45" t="n">
@@ -12079,10 +12091,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44085</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44089</v>
       </c>
       <c r="C46" t="n">
@@ -12111,10 +12123,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44180</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44182</v>
       </c>
       <c r="C47" t="n">
@@ -12143,10 +12155,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44271</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44273</v>
       </c>
       <c r="C48" t="n">
@@ -12175,10 +12187,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44392</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44396</v>
       </c>
       <c r="C49" t="n">
@@ -12207,10 +12219,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44456</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44460</v>
       </c>
       <c r="C50" t="n">
@@ -12239,10 +12251,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44544</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44546</v>
       </c>
       <c r="C51" t="n">
@@ -12271,10 +12283,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44635</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44637</v>
       </c>
       <c r="C52" t="n">
@@ -12303,10 +12315,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44756</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44760</v>
       </c>
       <c r="C53" t="n">
@@ -12335,10 +12347,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44824</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44826</v>
       </c>
       <c r="C54" t="n">
@@ -12367,10 +12379,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44911</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44915</v>
       </c>
       <c r="C55" t="n">
@@ -12399,10 +12411,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44999</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45001</v>
       </c>
       <c r="C56" t="n">
@@ -12431,10 +12443,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45120</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45124</v>
       </c>
       <c r="C57" t="n">
@@ -12463,10 +12475,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45189</v>
       </c>
       <c r="C58" t="n">
@@ -12495,10 +12507,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45278</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45279</v>
       </c>
       <c r="C59" t="n">
@@ -12527,10 +12539,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45370</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45372</v>
       </c>
       <c r="C60" t="n">
@@ -12559,10 +12571,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45484</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45488</v>
       </c>
       <c r="C61" t="n">
@@ -12591,10 +12603,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45552</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45554</v>
       </c>
       <c r="C62" t="n">
@@ -12623,10 +12635,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45643</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="C63" t="n">
@@ -12655,10 +12667,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45734</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="C64" t="n">
@@ -12687,10 +12699,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45855</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45859</v>
       </c>
       <c r="C65" t="n">
@@ -12719,10 +12731,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45916</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45918</v>
       </c>
       <c r="C66" t="n">
@@ -12751,10 +12763,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46007</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="C67" t="n">
@@ -12783,10 +12795,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46098</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46100</v>
       </c>
       <c r="C68" t="n">
@@ -12815,10 +12827,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46219</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46223</v>
       </c>
       <c r="C69" t="n">
@@ -12865,12 +12877,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/FDX.xlsx
+++ b/salidas/empresas/FDX.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>65.34454345703125</v>
+        <v>65.34453582763672</v>
       </c>
       <c r="C2" t="n">
         <v>81.50685119628906</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>73.01334381103516</v>
+        <v>73.01335906982422</v>
       </c>
       <c r="C4" t="n">
         <v>91.00725555419922</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>74.42916870117188</v>
+        <v>74.42913818359375</v>
       </c>
       <c r="C5" t="n">
         <v>92.77195739746094</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>70.6407470703125</v>
+        <v>70.64076232910156</v>
       </c>
       <c r="C6" t="n">
         <v>88.04995727539062</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>75.61069488525391</v>
+        <v>75.61073303222656</v>
       </c>
       <c r="C7" t="n">
         <v>94.16599273681641</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>67.74945068359375</v>
+        <v>67.74943542480469</v>
       </c>
       <c r="C8" t="n">
         <v>84.37550354003906</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>65.36839294433594</v>
+        <v>65.36837005615234</v>
       </c>
       <c r="C9" t="n">
         <v>81.41015625</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>70.3809814453125</v>
+        <v>70.38096618652344</v>
       </c>
       <c r="C10" t="n">
         <v>87.57453918457031</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>74.17587280273438</v>
+        <v>74.17586517333984</v>
       </c>
       <c r="C11" t="n">
         <v>92.29653167724609</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>74.75222015380859</v>
+        <v>74.75224304199219</v>
       </c>
       <c r="C12" t="n">
         <v>93.01370239257812</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>70.39636993408203</v>
+        <v>70.39634704589844</v>
       </c>
       <c r="C13" t="n">
         <v>87.52619171142578</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>71.54994201660156</v>
+        <v>71.54989624023438</v>
       </c>
       <c r="C14" t="n">
         <v>88.96051788330078</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>74.03214263916016</v>
+        <v>74.0321044921875</v>
       </c>
       <c r="C15" t="n">
         <v>92.04673767089844</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>69.68090057373047</v>
+        <v>69.68088531494141</v>
       </c>
       <c r="C16" t="n">
         <v>86.56728363037109</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>68.39013671875</v>
+        <v>68.39014434814453</v>
       </c>
       <c r="C17" t="n">
         <v>84.96373748779297</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>72.04293060302734</v>
+        <v>72.04290771484375</v>
       </c>
       <c r="C19" t="n">
         <v>89.41982269287109</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>71.89363098144531</v>
+        <v>71.89361572265625</v>
       </c>
       <c r="C20" t="n">
         <v>89.23448944091797</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>71.2054443359375</v>
+        <v>71.20547485351562</v>
       </c>
       <c r="C21" t="n">
         <v>88.38034057617188</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>68.06675720214844</v>
+        <v>68.0667724609375</v>
       </c>
       <c r="C22" t="n">
         <v>84.40773773193359</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>67.15052032470703</v>
+        <v>67.15055084228516</v>
       </c>
       <c r="C23" t="n">
         <v>83.27155303955078</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>63.98600387573242</v>
+        <v>63.98598480224609</v>
       </c>
       <c r="C24" t="n">
         <v>79.34729766845703</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>58.0007209777832</v>
+        <v>58.00070953369141</v>
       </c>
       <c r="C25" t="n">
         <v>71.85334777832031</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>60.70009994506836</v>
+        <v>60.70008850097656</v>
       </c>
       <c r="C26" t="n">
         <v>75.19741821289062</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>57.32426452636719</v>
+        <v>57.32426071166992</v>
       </c>
       <c r="C27" t="n">
         <v>71.01531219482422</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>60.34523010253906</v>
+        <v>60.34520721435547</v>
       </c>
       <c r="C28" t="n">
         <v>74.67365264892578</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>62.42902374267578</v>
+        <v>62.42900085449219</v>
       </c>
       <c r="C29" t="n">
         <v>77.25221252441406</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>51.36938095092773</v>
+        <v>51.36936569213867</v>
       </c>
       <c r="C31" t="n">
         <v>63.48912048339844</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>53.99684143066406</v>
+        <v>53.99685668945312</v>
       </c>
       <c r="C33" t="n">
         <v>66.73650360107422</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>51.60134124755859</v>
+        <v>51.60136032104492</v>
       </c>
       <c r="C34" t="n">
         <v>63.69057083129883</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>42.67687606811523</v>
+        <v>42.6768798828125</v>
       </c>
       <c r="C35" t="n">
         <v>52.67526245117188</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>46.12392807006836</v>
+        <v>46.12392425537109</v>
       </c>
       <c r="C36" t="n">
         <v>56.92989349365234</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>41.95291137695312</v>
+        <v>41.95289611816406</v>
       </c>
       <c r="C37" t="n">
         <v>51.69218444824219</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>33.31380462646484</v>
+        <v>33.31381225585938</v>
       </c>
       <c r="C38" t="n">
         <v>41.04754257202148</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>28.25853538513184</v>
+        <v>28.25853729248047</v>
       </c>
       <c r="C39" t="n">
         <v>34.81869506835938</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>36.36205291748047</v>
+        <v>36.36204147338867</v>
       </c>
       <c r="C42" t="n">
         <v>44.66559219360352</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>36.56401824951172</v>
+        <v>36.56401443481445</v>
       </c>
       <c r="C43" t="n">
         <v>44.81869506835938</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>45.16924667358398</v>
+        <v>45.16926193237305</v>
       </c>
       <c r="C45" t="n">
         <v>55.36663818359375</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>49.52572250366211</v>
+        <v>49.52573013305664</v>
       </c>
       <c r="C46" t="n">
         <v>60.61240768432617</v>
@@ -1359,7 +1359,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>47.85994720458984</v>
+        <v>47.85993194580078</v>
       </c>
       <c r="C47" t="n">
         <v>58.57373046875</v>
@@ -1384,7 +1384,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>55.60285186767578</v>
+        <v>55.60287094116211</v>
       </c>
       <c r="C48" t="n">
         <v>68.04995727539062</v>
@@ -1409,7 +1409,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>55.01246643066406</v>
+        <v>55.01245498657227</v>
       </c>
       <c r="C49" t="n">
         <v>67.24415588378906</v>
@@ -1434,7 +1434,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>51.65040588378906</v>
+        <v>51.650390625</v>
       </c>
       <c r="C50" t="n">
         <v>63.13456726074219</v>
@@ -1459,7 +1459,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>55.87604522705078</v>
+        <v>55.87602996826172</v>
       </c>
       <c r="C51" t="n">
         <v>68.29975891113281</v>
@@ -1484,7 +1484,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>61.64998245239258</v>
+        <v>61.64998626708984</v>
       </c>
       <c r="C52" t="n">
         <v>75.26188659667969</v>
@@ -1509,7 +1509,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>59.41239547729492</v>
+        <v>59.41238021850586</v>
       </c>
       <c r="C53" t="n">
         <v>72.53022003173828</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>55.1087532043457</v>
+        <v>55.1087646484375</v>
       </c>
       <c r="C54" t="n">
         <v>67.27639007568359</v>
@@ -1559,7 +1559,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>46.34537124633789</v>
+        <v>46.34535598754883</v>
       </c>
       <c r="C55" t="n">
         <v>56.4947624206543</v>
@@ -1584,7 +1584,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>54.56867599487305</v>
+        <v>54.56869125366211</v>
       </c>
       <c r="C56" t="n">
         <v>66.51893615722656</v>
@@ -1613,7 +1613,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>51.59401321411133</v>
+        <v>51.593994140625</v>
       </c>
       <c r="C57" t="n">
         <v>62.89282989501953</v>
@@ -1642,7 +1642,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>56.60157012939453</v>
+        <v>56.60159683227539</v>
       </c>
       <c r="C58" t="n">
         <v>68.89604949951172</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>58.07123947143555</v>
+        <v>58.07123184204102</v>
       </c>
       <c r="C59" t="n">
         <v>70.68492889404297</v>
@@ -1700,7 +1700,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>60.40671920776367</v>
+        <v>60.4067268371582</v>
       </c>
       <c r="C60" t="n">
         <v>73.42465972900391</v>
@@ -1758,7 +1758,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>59.87636566162109</v>
+        <v>59.87638092041016</v>
       </c>
       <c r="C62" t="n">
         <v>72.78001403808594</v>
@@ -1787,7 +1787,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>59.67751312255859</v>
+        <v>59.677490234375</v>
       </c>
       <c r="C63" t="n">
         <v>72.53827667236328</v>
@@ -1816,7 +1816,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>62.10256576538086</v>
+        <v>62.1025505065918</v>
       </c>
       <c r="C64" t="n">
         <v>75.38275909423828</v>
@@ -1845,7 +1845,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>63.50991821289062</v>
+        <v>63.50988388061523</v>
       </c>
       <c r="C65" t="n">
         <v>77.09105682373047</v>
@@ -1874,7 +1874,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>62.16228866577148</v>
+        <v>62.16229248046875</v>
       </c>
       <c r="C66" t="n">
         <v>75.45527648925781</v>
@@ -1903,7 +1903,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>63.05930328369141</v>
+        <v>63.0593147277832</v>
       </c>
       <c r="C67" t="n">
         <v>76.4302978515625</v>
@@ -1961,7 +1961,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>52.33556365966797</v>
+        <v>52.33556747436523</v>
       </c>
       <c r="C69" t="n">
         <v>63.43271636962891</v>
@@ -1990,7 +1990,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>45.07263946533203</v>
+        <v>45.07265090942383</v>
       </c>
       <c r="C70" t="n">
         <v>54.53666305541992</v>
@@ -2019,7 +2019,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>54.4960823059082</v>
+        <v>54.49609375</v>
       </c>
       <c r="C71" t="n">
         <v>65.93875885009766</v>
@@ -2048,7 +2048,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>55.32855224609375</v>
+        <v>55.32854080200195</v>
       </c>
       <c r="C72" t="n">
         <v>66.94601440429688</v>
@@ -2077,7 +2077,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>55.70270538330078</v>
+        <v>55.70270919799805</v>
       </c>
       <c r="C73" t="n">
         <v>67.29250335693359</v>
@@ -2106,7 +2106,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>61.0255012512207</v>
+        <v>61.02552795410156</v>
       </c>
       <c r="C74" t="n">
         <v>73.72280120849609</v>
@@ -2164,7 +2164,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>61.42797470092773</v>
+        <v>61.42798233032227</v>
       </c>
       <c r="C76" t="n">
         <v>74.10153198242188</v>
@@ -2193,7 +2193,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>58.94306945800781</v>
+        <v>58.94308090209961</v>
       </c>
       <c r="C77" t="n">
         <v>71.10395050048828</v>
@@ -2222,7 +2222,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>59.54424667358398</v>
+        <v>59.54427337646484</v>
       </c>
       <c r="C78" t="n">
         <v>71.82917022705078</v>
@@ -2251,7 +2251,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>61.29376220703125</v>
+        <v>61.29373550415039</v>
       </c>
       <c r="C79" t="n">
         <v>73.81950378417969</v>
@@ -2280,7 +2280,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>60.41725540161133</v>
+        <v>60.41726684570312</v>
       </c>
       <c r="C80" t="n">
         <v>72.76390075683594</v>
@@ -2309,7 +2309,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>58.63084411621094</v>
+        <v>58.63082885742188</v>
       </c>
       <c r="C81" t="n">
         <v>70.61241149902344</v>
@@ -2338,7 +2338,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>56.70944595336914</v>
+        <v>56.70946502685547</v>
       </c>
       <c r="C82" t="n">
         <v>68.18694305419922</v>
@@ -2367,7 +2367,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>61.64858627319336</v>
+        <v>61.64854431152344</v>
       </c>
       <c r="C83" t="n">
         <v>74.12570190429688</v>
@@ -2396,7 +2396,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>60.09763336181641</v>
+        <v>60.09764862060547</v>
       </c>
       <c r="C84" t="n">
         <v>72.1434326171875</v>
@@ -2425,7 +2425,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>61.56773376464844</v>
+        <v>61.56771469116211</v>
       </c>
       <c r="C85" t="n">
         <v>73.90814208984375</v>
@@ -2454,7 +2454,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>68.09900665283203</v>
+        <v>68.09903717041016</v>
       </c>
       <c r="C86" t="n">
         <v>81.74858856201172</v>
@@ -2483,7 +2483,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>70.77064514160156</v>
+        <v>70.7706298828125</v>
       </c>
       <c r="C87" t="n">
         <v>84.95568084716797</v>
@@ -2512,7 +2512,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>66.00299072265625</v>
+        <v>66.00297546386719</v>
       </c>
       <c r="C88" t="n">
         <v>79.12973022460938</v>
@@ -2541,7 +2541,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>63.186767578125</v>
+        <v>63.1867561340332</v>
       </c>
       <c r="C89" t="n">
         <v>75.75342559814453</v>
@@ -2570,7 +2570,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>64.75283813476562</v>
+        <v>64.75283050537109</v>
       </c>
       <c r="C90" t="n">
         <v>77.63094329833984</v>
@@ -2628,7 +2628,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>71.35539245605469</v>
+        <v>71.35538482666016</v>
       </c>
       <c r="C92" t="n">
         <v>85.41498565673828</v>
@@ -2657,7 +2657,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>72.27088165283203</v>
+        <v>72.2708740234375</v>
       </c>
       <c r="C93" t="n">
         <v>86.51087951660156</v>
@@ -2686,7 +2686,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>76.9205322265625</v>
+        <v>76.92054748535156</v>
       </c>
       <c r="C94" t="n">
         <v>91.95004272460938</v>
@@ -2744,7 +2744,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>93.49645233154297</v>
+        <v>93.49642944335938</v>
       </c>
       <c r="C96" t="n">
         <v>111.7647094726562</v>
@@ -2773,7 +2773,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>97.01817321777344</v>
+        <v>97.01815032958984</v>
       </c>
       <c r="C97" t="n">
         <v>115.8501205444336</v>
@@ -2802,7 +2802,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>89.96633148193359</v>
+        <v>89.96632385253906</v>
       </c>
       <c r="C98" t="n">
         <v>107.4294891357422</v>
@@ -2860,7 +2860,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>89.55132293701172</v>
+        <v>89.55135345458984</v>
       </c>
       <c r="C100" t="n">
         <v>106.8170852661133</v>
@@ -2889,7 +2889,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>92.04409790039062</v>
+        <v>92.04411315917969</v>
       </c>
       <c r="C101" t="n">
         <v>109.7904891967773</v>
@@ -2918,7 +2918,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>97.38776397705078</v>
+        <v>97.38773345947266</v>
       </c>
       <c r="C102" t="n">
         <v>116.1643829345703</v>
@@ -2947,7 +2947,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>102.4121170043945</v>
+        <v>102.412109375</v>
       </c>
       <c r="C103" t="n">
         <v>121.9822692871094</v>
@@ -2976,7 +2976,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>99.36775207519531</v>
+        <v>99.36779022216797</v>
       </c>
       <c r="C104" t="n">
         <v>118.3561630249023</v>
@@ -3005,7 +3005,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>100.044319152832</v>
+        <v>100.0442733764648</v>
       </c>
       <c r="C105" t="n">
         <v>119.1619644165039</v>
@@ -3034,7 +3034,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>109.3673858642578</v>
+        <v>109.3673782348633</v>
       </c>
       <c r="C106" t="n">
         <v>130.0966949462891</v>
@@ -3063,7 +3063,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>113.3979415893555</v>
+        <v>113.3979644775391</v>
       </c>
       <c r="C107" t="n">
         <v>134.8912200927734</v>
@@ -3092,7 +3092,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>120.7004318237305</v>
+        <v>120.7004470825195</v>
       </c>
       <c r="C108" t="n">
         <v>143.5777587890625</v>
@@ -3121,7 +3121,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>117.7702941894531</v>
+        <v>117.7703018188477</v>
       </c>
       <c r="C109" t="n">
         <v>139.9355316162109</v>
@@ -3150,7 +3150,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>114.6846466064453</v>
+        <v>114.6846389770508</v>
       </c>
       <c r="C110" t="n">
         <v>136.2691345214844</v>
@@ -3179,7 +3179,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>120.0218048095703</v>
+        <v>120.0218200683594</v>
       </c>
       <c r="C111" t="n">
         <v>142.6107940673828</v>
@@ -3208,7 +3208,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>112.3322677612305</v>
+        <v>112.332275390625</v>
       </c>
       <c r="C112" t="n">
         <v>133.3199005126953</v>
@@ -3237,7 +3237,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>115.1295700073242</v>
+        <v>115.1295623779297</v>
       </c>
       <c r="C113" t="n">
         <v>136.6398010253906</v>
@@ -3266,7 +3266,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>117.6077117919922</v>
+        <v>117.6077041625977</v>
       </c>
       <c r="C114" t="n">
         <v>139.5809783935547</v>
@@ -3295,7 +3295,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>115.8516387939453</v>
+        <v>115.8516464233398</v>
       </c>
       <c r="C115" t="n">
         <v>137.3086242675781</v>
@@ -3324,7 +3324,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>116.5450744628906</v>
+        <v>116.5451354980469</v>
       </c>
       <c r="C116" t="n">
         <v>138.1305389404297</v>
@@ -3353,7 +3353,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>102.3968048095703</v>
+        <v>102.3967895507812</v>
       </c>
       <c r="C117" t="n">
         <v>121.3618087768555</v>
@@ -3382,7 +3382,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>98.05413055419922</v>
+        <v>98.05414581298828</v>
       </c>
       <c r="C118" t="n">
         <v>116.0193405151367</v>
@@ -3440,7 +3440,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>107.9698638916016</v>
+        <v>107.9699020385742</v>
       </c>
       <c r="C120" t="n">
         <v>127.7518157958984</v>
@@ -3469,7 +3469,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>101.6388854980469</v>
+        <v>101.6388931274414</v>
       </c>
       <c r="C121" t="n">
         <v>120.0564041137695</v>
@@ -3498,7 +3498,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>90.64887237548828</v>
+        <v>90.64888000488281</v>
       </c>
       <c r="C122" t="n">
         <v>107.0749435424805</v>
@@ -3527,7 +3527,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>93.37762451171875</v>
+        <v>93.37760925292969</v>
       </c>
       <c r="C123" t="n">
         <v>110.2981491088867</v>
@@ -3556,7 +3556,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>111.2011260986328</v>
+        <v>111.2010803222656</v>
       </c>
       <c r="C124" t="n">
         <v>131.1200714111328</v>
@@ -3585,7 +3585,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>112.8344116210938</v>
+        <v>112.8343963623047</v>
       </c>
       <c r="C125" t="n">
         <v>133.0459289550781</v>
@@ -3614,7 +3614,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>112.7387084960938</v>
+        <v>112.7387161254883</v>
       </c>
       <c r="C126" t="n">
         <v>132.9331207275391</v>
@@ -3672,7 +3672,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>110.9172821044922</v>
+        <v>110.9172668457031</v>
       </c>
       <c r="C128" t="n">
         <v>130.4593048095703</v>
@@ -3701,7 +3701,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>112.9930801391602</v>
+        <v>112.9931030273438</v>
       </c>
       <c r="C129" t="n">
         <v>132.90087890625</v>
@@ -3730,7 +3730,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>119.9632797241211</v>
+        <v>119.9633102416992</v>
       </c>
       <c r="C130" t="n">
         <v>140.7574615478516</v>
@@ -3759,7 +3759,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>119.7160491943359</v>
+        <v>119.716064453125</v>
       </c>
       <c r="C131" t="n">
         <v>140.4673614501953</v>
@@ -3788,7 +3788,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>131.6313323974609</v>
+        <v>131.6313781738281</v>
       </c>
       <c r="C132" t="n">
         <v>154.4480285644531</v>
@@ -3817,7 +3817,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>128.1355895996094</v>
+        <v>128.135498046875</v>
       </c>
       <c r="C133" t="n">
         <v>150.040283203125</v>
@@ -3846,7 +3846,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>130.1381225585938</v>
+        <v>130.1381072998047</v>
       </c>
       <c r="C134" t="n">
         <v>152.3851776123047</v>
@@ -3875,7 +3875,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>132.8013153076172</v>
+        <v>132.8013000488281</v>
       </c>
       <c r="C135" t="n">
         <v>155.5036315917969</v>
@@ -3904,7 +3904,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>134.5736694335938</v>
+        <v>134.5735931396484</v>
       </c>
       <c r="C136" t="n">
         <v>157.2522125244141</v>
@@ -3933,7 +3933,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>130.8153533935547</v>
+        <v>130.8153381347656</v>
       </c>
       <c r="C137" t="n">
         <v>152.860595703125</v>
@@ -3991,7 +3991,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>150.2248687744141</v>
+        <v>150.224853515625</v>
       </c>
       <c r="C139" t="n">
         <v>175.1248931884766</v>
@@ -4020,7 +4020,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>143.7963562011719</v>
+        <v>143.7964019775391</v>
       </c>
       <c r="C140" t="n">
         <v>167.6309356689453</v>
@@ -4049,7 +4049,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>148.1857147216797</v>
+        <v>148.1857452392578</v>
       </c>
       <c r="C141" t="n">
         <v>172.7477874755859</v>
@@ -4078,7 +4078,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>156.2931671142578</v>
+        <v>156.2932281494141</v>
       </c>
       <c r="C142" t="n">
         <v>181.7727661132812</v>
@@ -4136,7 +4136,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>160.3672027587891</v>
+        <v>160.3672180175781</v>
       </c>
       <c r="C144" t="n">
         <v>186.5108795166016</v>
@@ -4165,7 +4165,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>173.2559204101562</v>
+        <v>173.2559509277344</v>
       </c>
       <c r="C145" t="n">
         <v>201.0797729492188</v>
@@ -4194,7 +4194,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>182.2401428222656</v>
+        <v>182.2401885986328</v>
       </c>
       <c r="C146" t="n">
         <v>211.5068511962891</v>
@@ -4252,7 +4252,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>167.0560455322266</v>
+        <v>167.0560150146484</v>
       </c>
       <c r="C148" t="n">
         <v>193.4810638427734</v>
@@ -4281,7 +4281,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>171.9888763427734</v>
+        <v>171.9888610839844</v>
       </c>
       <c r="C149" t="n">
         <v>199.1941986083984</v>
@@ -4339,7 +4339,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>158.3937683105469</v>
+        <v>158.3938293457031</v>
       </c>
       <c r="C151" t="n">
         <v>182.9653472900391</v>
@@ -4368,7 +4368,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>171.5154113769531</v>
+        <v>171.515380859375</v>
       </c>
       <c r="C152" t="n">
         <v>198.1224822998047</v>
@@ -4397,7 +4397,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>170.1760406494141</v>
+        <v>170.176025390625</v>
       </c>
       <c r="C153" t="n">
         <v>196.5753479003906</v>
@@ -4426,7 +4426,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>168.4162750244141</v>
+        <v>168.4163513183594</v>
       </c>
       <c r="C154" t="n">
         <v>194.0290069580078</v>
@@ -4455,7 +4455,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>154.1129455566406</v>
+        <v>154.1129608154297</v>
       </c>
       <c r="C155" t="n">
         <v>177.5503692626953</v>
@@ -4484,7 +4484,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>160.1700439453125</v>
+        <v>160.1700592041016</v>
       </c>
       <c r="C156" t="n">
         <v>184.5286102294922</v>
@@ -4513,7 +4513,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>113.1815032958984</v>
+        <v>113.181510925293</v>
       </c>
       <c r="C157" t="n">
         <v>130</v>
@@ -4542,7 +4542,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>124.5747451782227</v>
+        <v>124.5747222900391</v>
       </c>
       <c r="C158" t="n">
         <v>143.0862274169922</v>
@@ -4571,7 +4571,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>126.981071472168</v>
+        <v>126.9810943603516</v>
       </c>
       <c r="C159" t="n">
         <v>145.8501281738281</v>
@@ -4629,7 +4629,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>133.4178771972656</v>
+        <v>133.4178466796875</v>
       </c>
       <c r="C161" t="n">
         <v>152.6672058105469</v>
@@ -4658,7 +4658,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>108.6440963745117</v>
+        <v>108.6441116333008</v>
       </c>
       <c r="C162" t="n">
         <v>124.3190994262695</v>
@@ -4687,7 +4687,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>116.0704650878906</v>
+        <v>116.0704803466797</v>
       </c>
       <c r="C163" t="n">
         <v>132.3045959472656</v>
@@ -4716,7 +4716,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>120.5523910522461</v>
+        <v>120.5523986816406</v>
       </c>
       <c r="C164" t="n">
         <v>137.4133758544922</v>
@@ -4803,7 +4803,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>108.3480453491211</v>
+        <v>108.348030090332</v>
       </c>
       <c r="C167" t="n">
         <v>123.0137023925781</v>
@@ -4832,7 +4832,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>113.5929718017578</v>
+        <v>113.5929489135742</v>
       </c>
       <c r="C168" t="n">
         <v>128.9685668945312</v>
@@ -4861,7 +4861,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>107.7739639282227</v>
+        <v>107.7739791870117</v>
       </c>
       <c r="C169" t="n">
         <v>121.8452835083008</v>
@@ -4948,7 +4948,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>86.86184692382812</v>
+        <v>86.86183929443359</v>
       </c>
       <c r="C172" t="n">
         <v>97.71152496337891</v>
@@ -4975,7 +4975,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>90.80882263183594</v>
+        <v>90.80881500244141</v>
       </c>
       <c r="C173" t="n">
         <v>102.1514892578125</v>
@@ -5029,7 +5029,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>100.9253692626953</v>
+        <v>100.9253768920898</v>
       </c>
       <c r="C175" t="n">
         <v>112.9895248413086</v>
@@ -5056,7 +5056,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>121.2083435058594</v>
+        <v>121.2083587646484</v>
       </c>
       <c r="C176" t="n">
         <v>135.697021484375</v>
@@ -5114,7 +5114,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>181.5529479980469</v>
+        <v>181.5529632568359</v>
       </c>
       <c r="C178" t="n">
         <v>202.6752624511719</v>
@@ -5143,7 +5143,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>187.2914276123047</v>
+        <v>187.2914886474609</v>
       </c>
       <c r="C179" t="n">
         <v>209.0813903808594</v>
@@ -5201,7 +5201,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>187.8194122314453</v>
+        <v>187.8193817138672</v>
       </c>
       <c r="C181" t="n">
         <v>209.2022552490234</v>
@@ -5230,7 +5230,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>170.2542877197266</v>
+        <v>170.2543334960938</v>
       </c>
       <c r="C182" t="n">
         <v>189.6373901367188</v>
@@ -5259,7 +5259,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>184.1154327392578</v>
+        <v>184.1154022216797</v>
       </c>
       <c r="C183" t="n">
         <v>205.0765533447266</v>
@@ -5288,7 +5288,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>206.0207977294922</v>
+        <v>206.0207824707031</v>
       </c>
       <c r="C184" t="n">
         <v>228.8799285888672</v>
@@ -5317,7 +5317,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>210.5685577392578</v>
+        <v>210.568603515625</v>
       </c>
       <c r="C185" t="n">
         <v>233.9323120117188</v>
@@ -5346,7 +5346,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>228.3390045166016</v>
+        <v>228.3390197753906</v>
       </c>
       <c r="C186" t="n">
         <v>253.6744537353516</v>
@@ -5375,7 +5375,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>216.9213714599609</v>
+        <v>216.92138671875</v>
       </c>
       <c r="C187" t="n">
         <v>240.3948364257812</v>
@@ -5404,7 +5404,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>203.5569305419922</v>
+        <v>203.5569458007812</v>
       </c>
       <c r="C188" t="n">
         <v>225.5842132568359</v>
@@ -5462,7 +5462,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>159.90087890625</v>
+        <v>159.9008636474609</v>
       </c>
       <c r="C190" t="n">
         <v>176.7042694091797</v>
@@ -5491,7 +5491,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>171.74267578125</v>
+        <v>171.7426910400391</v>
       </c>
       <c r="C191" t="n">
         <v>189.7904968261719</v>
@@ -5520,7 +5520,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>167.9801635742188</v>
+        <v>167.9801330566406</v>
       </c>
       <c r="C192" t="n">
         <v>185.6325531005859</v>
@@ -5549,7 +5549,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>189.1724395751953</v>
+        <v>189.1724243164062</v>
       </c>
       <c r="C193" t="n">
         <v>208.4125671386719</v>
@@ -5578,7 +5578,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>179.8250122070312</v>
+        <v>179.8249969482422</v>
       </c>
       <c r="C194" t="n">
         <v>198.1144256591797</v>
@@ -5607,7 +5607,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>162.5709686279297</v>
+        <v>162.5709533691406</v>
       </c>
       <c r="C195" t="n">
         <v>179.1055603027344</v>
@@ -5636,7 +5636,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>169.8169097900391</v>
+        <v>169.8169250488281</v>
       </c>
       <c r="C196" t="n">
         <v>186.4544677734375</v>
@@ -5665,7 +5665,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>145.8551177978516</v>
+        <v>145.8551330566406</v>
       </c>
       <c r="C197" t="n">
         <v>160.1450500488281</v>
@@ -5694,7 +5694,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>164.819091796875</v>
+        <v>164.8190612792969</v>
       </c>
       <c r="C198" t="n">
         <v>180.9669647216797</v>
@@ -5723,7 +5723,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>167.2252655029297</v>
+        <v>167.2252502441406</v>
       </c>
       <c r="C199" t="n">
         <v>182.6833190917969</v>
@@ -5781,7 +5781,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>155.4971466064453</v>
+        <v>155.4971618652344</v>
       </c>
       <c r="C201" t="n">
         <v>169.8710784912109</v>
@@ -5810,7 +5810,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>110.1147689819336</v>
+        <v>110.1147766113281</v>
       </c>
       <c r="C202" t="n">
         <v>119.6373901367188</v>
@@ -5839,7 +5839,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>118.8738098144531</v>
+        <v>118.8738403320312</v>
       </c>
       <c r="C203" t="n">
         <v>129.1539154052734</v>
@@ -5868,7 +5868,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>135.1459503173828</v>
+        <v>135.1459197998047</v>
       </c>
       <c r="C204" t="n">
         <v>146.8332061767578</v>
@@ -5897,7 +5897,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>129.3211975097656</v>
+        <v>129.3211822509766</v>
       </c>
       <c r="C205" t="n">
         <v>139.5648651123047</v>
@@ -5926,7 +5926,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>144.7471466064453</v>
+        <v>144.7471313476562</v>
       </c>
       <c r="C206" t="n">
         <v>156.2127380371094</v>
@@ -5955,7 +5955,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>151.7358703613281</v>
+        <v>151.7358856201172</v>
       </c>
       <c r="C207" t="n">
         <v>163.7550354003906</v>
@@ -5984,7 +5984,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>171.55322265625</v>
+        <v>171.5532073974609</v>
       </c>
       <c r="C208" t="n">
         <v>184.1176452636719</v>
@@ -6042,7 +6042,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>163.6621856689453</v>
+        <v>163.6621704101562</v>
       </c>
       <c r="C210" t="n">
         <v>175.6486663818359</v>
@@ -6071,7 +6071,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>187.1745910644531</v>
+        <v>187.1746215820312</v>
       </c>
       <c r="C211" t="n">
         <v>199.7582550048828</v>
@@ -6129,7 +6129,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>197.0807342529297</v>
+        <v>197.0807495117188</v>
       </c>
       <c r="C213" t="n">
         <v>210.3303833007812</v>
@@ -6216,7 +6216,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>196.3932495117188</v>
+        <v>196.3932342529297</v>
       </c>
       <c r="C216" t="n">
         <v>208.565673828125</v>
@@ -6245,7 +6245,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>192.8547821044922</v>
+        <v>192.8548126220703</v>
       </c>
       <c r="C217" t="n">
         <v>203.8436737060547</v>
@@ -6274,7 +6274,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>183.9504089355469</v>
+        <v>183.9503936767578</v>
       </c>
       <c r="C218" t="n">
         <v>194.4319152832031</v>
@@ -6332,7 +6332,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>222.0046997070312</v>
+        <v>222.0046539306641</v>
       </c>
       <c r="C220" t="n">
         <v>233.4730072021484</v>
@@ -6361,7 +6361,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>200.5811614990234</v>
+        <v>200.5811767578125</v>
       </c>
       <c r="C221" t="n">
         <v>210.9427947998047</v>
@@ -6390,7 +6390,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>194.5893249511719</v>
+        <v>194.5893096923828</v>
       </c>
       <c r="C222" t="n">
         <v>204.6414184570312</v>
@@ -6419,7 +6419,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>231.000244140625</v>
+        <v>231.0002136230469</v>
       </c>
       <c r="C223" t="n">
         <v>241.6116027832031</v>
@@ -6448,7 +6448,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>232.8569488525391</v>
+        <v>232.8569183349609</v>
       </c>
       <c r="C224" t="n">
         <v>243.5535888671875</v>
@@ -6477,7 +6477,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>230.1758575439453</v>
+        <v>230.1758880615234</v>
       </c>
       <c r="C225" t="n">
         <v>240.7493896484375</v>
@@ -6593,7 +6593,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>218.8779754638672</v>
+        <v>218.8780059814453</v>
       </c>
       <c r="C229" t="n">
         <v>226.6962127685547</v>
@@ -6622,7 +6622,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>206.0718841552734</v>
+        <v>206.0718994140625</v>
       </c>
       <c r="C230" t="n">
         <v>213.4327087402344</v>
@@ -6651,7 +6651,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>204.5392303466797</v>
+        <v>204.5392150878906</v>
       </c>
       <c r="C231" t="n">
         <v>211.8452911376953</v>
@@ -6709,7 +6709,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>164.5333404541016</v>
+        <v>164.5333557128906</v>
       </c>
       <c r="C233" t="n">
         <v>169.4842834472656</v>
@@ -6796,7 +6796,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>175.9566650390625</v>
+        <v>175.9566497802734</v>
       </c>
       <c r="C236" t="n">
         <v>180.0886383056641</v>
@@ -6854,7 +6854,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>186.8460845947266</v>
+        <v>186.8460998535156</v>
       </c>
       <c r="C238" t="n">
         <v>190.01611328125</v>
@@ -6970,7 +6970,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>256.6463317871094</v>
+        <v>256.6463623046875</v>
       </c>
       <c r="C242" t="n">
         <v>259.6696166992188</v>
@@ -7057,7 +7057,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>322.5064086914062</v>
+        <v>322.5063781738281</v>
       </c>
       <c r="C245" t="n">
         <v>324.9879150390625</v>
